--- a/KatalonData/ABPTestDataDemo/ABPEditUser.xlsx
+++ b/KatalonData/ABPTestDataDemo/ABPEditUser.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="38">
   <si>
     <t>Result</t>
   </si>
@@ -151,6 +151,12 @@
   </si>
   <si>
     <t>Fri Sep 18 02:29:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 20:54:37 IST 2026</t>
+  </si>
+  <si>
+    <t>2026-09-25 18:15:18</t>
   </si>
 </sst>
 </file>
@@ -855,7 +861,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>19</v>
@@ -1012,7 +1018,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>

--- a/KatalonData/ABPTestDataDemo/ABPEditUser.xlsx
+++ b/KatalonData/ABPTestDataDemo/ABPEditUser.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="48">
   <si>
     <t>Result</t>
   </si>
@@ -157,6 +157,36 @@
   </si>
   <si>
     <t>2026-09-25 18:15:18</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:04:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:04:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:04:56 IST 2026</t>
+  </si>
+  <si>
+    <t>2026-10-08 02:05:24</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:07:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:07:58 IST 2026</t>
+  </si>
+  <si>
+    <t>2026-10-08 02:08:28</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:10:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:11:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 19:23:37 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -617,7 +647,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>21</v>
@@ -704,7 +734,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>21</v>
@@ -791,7 +821,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>17</v>
@@ -861,7 +891,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>19</v>
@@ -948,7 +978,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>18</v>
@@ -1018,7 +1048,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -1088,7 +1118,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>20</v>
@@ -1175,7 +1205,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>12</v>
